--- a/results/Int Task Remove ACC -0.3/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.3/Linea_fi_all.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.018249304051964087 +/- 0.002787226805089714</t>
+          <t>0.018218373028147196 +/- 0.0027472948587425427</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-0.004900411002213045 +/- 0.0014226999683844455</t>
+          <t>-0.0049004110022130565 +/- 0.0014710578721633674</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.0019285488460322187 +/- 0.0015388041130114333</t>
+          <t>-0.0019601644008852004 +/- 0.0015016556543835501</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.006481188744862465 +/- 0.0014366826136581502</t>
+          <t>-0.006449573190009472 +/- 0.0014011077967853536</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.12976758993950968 +/- 0.004967387421799969</t>
+          <t>0.1298312639286851 +/- 0.004886330478942932</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0709328239414199 +/- 0.0049461207223020455</t>
+          <t>0.07096466093600762 +/- 0.004906307087285862</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.04988864142538975 +/- 0.0036131262021198555</t>
+          <t>0.04992045816099268 +/- 0.0036344963290808707</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.036308958531180824 +/- 0.005689293751472046</t>
+          <t>0.03627730294396969 +/- 0.005671918051136451</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.00020408163265305256 +/- 0.0011703843900738276</t>
+          <t>-0.00023809523809522614 +/- 0.0011982255070618036</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.00020408163265304147 +/- 0.007421204390649961</t>
+          <t>-0.00023809523809521506 +/- 0.007447426297218157</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4471,72 +4471,72 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>-0.0007416962270234805 +/- 0.0006923866673197022</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0394388906804257 +/- 0.004122280583558598</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-0.005965817478232771 +/- 0.003913144501616117</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-0.005965817478232771 +/- 0.003913144501616117</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.02586262495969046 +/- 0.002333447599500239</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-0.001064172847468503 +/- 0.003089891484349491</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.014092228313447318 +/- 0.003848296067635357</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.00016123831022254453 +/- 0.0036176358076551187</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0.008997097710416036 +/- 0.0020970900339102264</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0.011125443405353153 +/- 0.0025646523251510412</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.40232183166720425 +/- 0.007502278403783436</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0.00986778458561759 +/- 0.0020354380958477274</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0.09093840696549504 +/- 0.00749784148262723</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>-0.0007739438890679851 +/- 0.0006946358990176756</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.0394388906804257 +/- 0.004122280583558598</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-0.005965817478232771 +/- 0.003913144501616117</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-0.005965817478232771 +/- 0.003913144501616117</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.02586262495969046 +/- 0.002333447599500239</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-0.001064172847468503 +/- 0.003089891484349491</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.014092228313447318 +/- 0.003848296067635357</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.00016123831022254453 +/- 0.0036176358076551187</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.008997097710416036 +/- 0.0020970900339102264</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.011125443405353153 +/- 0.0025646523251510412</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.40232183166720425 +/- 0.007502278403783436</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.00986778458561759 +/- 0.0020354380958477274</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.09093840696549504 +/- 0.00749784148262723</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>-0.0007416962270234805 +/- 0.0006923866673197022</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
+          <t>-0.0002563280999679951 +/- 0.0007555159322365643</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
           <t>-0.0002883691124639931 +/- 0.0007776136558482311</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>-0.0002563280999679951 +/- 0.0007555159322365643</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
